--- a/AAAGameData/DataTables/Core/ArrowUIGroupTable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUIGroupTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\arrowNew\AAAGameData\DataTables\Core\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\Core\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="16575"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,14 +97,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,148 +555,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1141,7 +1134,7 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1155,7 +1148,7 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1169,7 +1162,7 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
